--- a/MQTT_Sensor_Test_Cases.xlsx
+++ b/MQTT_Sensor_Test_Cases.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\Code Projects\CarIoT_Test_Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D30066D0-8FAC-4648-877D-F2D968E07F37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B444A560-CF44-435F-AD48-7B0DD45CBB02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16530" yWindow="-16200" windowWidth="18675" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20595" yWindow="-16200" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -567,7 +567,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -578,16 +578,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -870,7 +867,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="14.33203125" style="3" bestFit="1" customWidth="1"/>
@@ -884,7 +881,7 @@
     <col min="9" max="16384" width="9.06640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="22.15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" ht="22.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -910,7 +907,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="41.65" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:8" ht="41.65" x14ac:dyDescent="0.4">
       <c r="A2" s="5" t="s">
         <v>25</v>
       </c>
@@ -936,7 +933,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="5"/>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
@@ -948,7 +945,7 @@
       <c r="G3" s="5"/>
       <c r="H3" s="5"/>
     </row>
-    <row r="4" spans="1:9" ht="41.65" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:8" ht="41.65" x14ac:dyDescent="0.4">
       <c r="A4" s="5" t="s">
         <v>67</v>
       </c>
@@ -973,9 +970,8 @@
       <c r="H4" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="I4" s="4"/>
-    </row>
-    <row r="5" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="5" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="5"/>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -986,9 +982,8 @@
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
-      <c r="I5" s="4"/>
-    </row>
-    <row r="6" spans="1:9" ht="36.4" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="6" spans="1:8" ht="36.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="5" t="s">
         <v>70</v>
       </c>
@@ -1013,9 +1008,8 @@
       <c r="H6" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="I6" s="4"/>
-    </row>
-    <row r="7" spans="1:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="7" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="5"/>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
@@ -1026,9 +1020,8 @@
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
       <c r="H7" s="5"/>
-      <c r="I7" s="4"/>
-    </row>
-    <row r="8" spans="1:9" ht="41.65" x14ac:dyDescent="0.4">
+    </row>
+    <row r="8" spans="1:8" ht="41.65" x14ac:dyDescent="0.4">
       <c r="A8" s="3" t="s">
         <v>8</v>
       </c>
@@ -1054,7 +1047,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="3" t="s">
         <v>9</v>
       </c>
@@ -1080,7 +1073,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="3" t="s">
         <v>10</v>
       </c>
@@ -1106,7 +1099,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="41.65" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:8" ht="41.65" x14ac:dyDescent="0.4">
       <c r="A11" s="3" t="s">
         <v>11</v>
       </c>
@@ -1132,7 +1125,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="41.65" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:8" ht="41.65" x14ac:dyDescent="0.4">
       <c r="A12" s="3" t="s">
         <v>12</v>
       </c>
@@ -1158,7 +1151,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="27.75" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:8" ht="27.75" x14ac:dyDescent="0.4">
       <c r="A13" s="3" t="s">
         <v>13</v>
       </c>
@@ -1184,7 +1177,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="27.75" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:8" ht="27.75" x14ac:dyDescent="0.4">
       <c r="A14" s="3" t="s">
         <v>14</v>
       </c>
@@ -1210,303 +1203,309 @@
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="41.65" x14ac:dyDescent="0.4">
-      <c r="A15" s="6" t="s">
+    <row r="15" spans="1:8" ht="41.65" x14ac:dyDescent="0.4">
+      <c r="A15" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="F15" s="6" t="s">
+      <c r="F15" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="G15" s="6" t="s">
+      <c r="G15" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H15" s="6" t="s">
+      <c r="H15" s="4" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A16" s="7" t="s">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A16" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="F16" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="G16" s="7" t="s">
+      <c r="G16" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="H16" s="7" t="s">
+      <c r="H16" s="6" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="6" t="s">
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
     </row>
     <row r="18" spans="1:8" ht="41.65" x14ac:dyDescent="0.4">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E18" s="6" t="s">
+      <c r="E18" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="F18" s="6" t="s">
+      <c r="F18" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="G18" s="6" t="s">
+      <c r="G18" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="H18" s="6" t="s">
+      <c r="H18" s="4" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="41.65" x14ac:dyDescent="0.4">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D19" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="E19" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="F19" s="6" t="s">
+      <c r="F19" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="G19" s="6" t="s">
+      <c r="G19" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="H19" s="6" t="s">
+      <c r="H19" s="4" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="E20" s="6" t="s">
+      <c r="E20" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="F20" s="7" t="s">
+      <c r="F20" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="G20" s="7" t="s">
+      <c r="G20" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="H20" s="7" t="s">
+      <c r="H20" s="6" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="6" t="s">
+      <c r="A21" s="6"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
     </row>
     <row r="22" spans="1:8" ht="41.65" x14ac:dyDescent="0.4">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="D22" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E22" s="6" t="s">
+      <c r="E22" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="F22" s="6" t="s">
+      <c r="F22" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="G22" s="6" t="s">
+      <c r="G22" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="H22" s="6" t="s">
+      <c r="H22" s="4" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="D23" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E23" s="6" t="s">
+      <c r="E23" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="F23" s="6" t="s">
+      <c r="F23" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="G23" s="6" t="s">
+      <c r="G23" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="H23" s="6" t="s">
+      <c r="H23" s="4" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="46.15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="D24" s="6" t="s">
+      <c r="D24" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E24" s="6" t="s">
+      <c r="E24" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="F24" s="6" t="s">
+      <c r="F24" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="G24" s="6" t="s">
+      <c r="G24" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H24" s="6" t="s">
+      <c r="H24" s="4" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="41.65" x14ac:dyDescent="0.4">
-      <c r="A25" s="6" t="s">
+      <c r="A25" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D25" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E25" s="6" t="s">
+      <c r="E25" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="F25" s="6" t="s">
+      <c r="F25" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="G25" s="6" t="s">
+      <c r="G25" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="H25" s="6" t="s">
+      <c r="H25" s="4" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="41.65" x14ac:dyDescent="0.4">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C26" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="D26" s="6" t="s">
+      <c r="D26" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="E26" s="6" t="s">
+      <c r="E26" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="F26" s="6" t="s">
+      <c r="F26" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="G26" s="6" t="s">
+      <c r="G26" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="H26" s="6" t="s">
+      <c r="H26" s="4" t="s">
         <v>119</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="H6:H7"/>
     <mergeCell ref="D4:D5"/>
     <mergeCell ref="D6:D7"/>
     <mergeCell ref="G20:G21"/>
@@ -1514,23 +1513,17 @@
     <mergeCell ref="H2:H3"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="F2:F3"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A4:A5"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
